--- a/data/trans_dic/P16A11-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P16A11-Edad-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicinas para la tensión arterial en las dos últimas semanas</t>
+          <t>Población que ha consumido medicinas para la tensión arterial en las dos últimas semanas (tasa de respuesta: 99,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,79</t>
+          <t>0,0; 0,8</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,19</t>
+          <t>0,0; 1,07</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,23</t>
+          <t>0,0; 0,21</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,39</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,46</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,15</t>
+          <t>0,0; 1,14</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,55</t>
+          <t>0,0; 2,84</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,38</t>
+          <t>0,0; 0,45</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,8</t>
+          <t>0,0; 0,52</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,49</t>
+          <t>0,0; 0,56</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,02; 1,44</t>
+          <t>0,0; 1,45</t>
         </is>
       </c>
     </row>
@@ -857,32 +857,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,73</t>
+          <t>0,0; 0,85</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,41; 2,06</t>
+          <t>0,34; 2,01</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,33; 2,21</t>
+          <t>0,33; 2,07</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,68</t>
+          <t>0,0; 1,67</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,28; 1,65</t>
+          <t>0,28; 1,71</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,62; 2,89</t>
+          <t>0,63; 2,76</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -892,27 +892,27 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,32; 2,1</t>
+          <t>0,25; 2,11</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,2; 1,01</t>
+          <t>0,2; 0,96</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,62; 2,11</t>
+          <t>0,67; 2,05</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,25; 1,35</t>
+          <t>0,25; 1,28</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,28; 1,41</t>
+          <t>0,31; 1,44</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,64; 4,05</t>
+          <t>1,49; 3,99</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,14; 6,42</t>
+          <t>3,13; 6,45</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,95; 4,64</t>
+          <t>1,99; 4,76</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,18; 5,47</t>
+          <t>2,07; 5,39</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,79; 5,81</t>
+          <t>2,82; 5,8</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,05; 4,68</t>
+          <t>2,06; 4,68</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,34; 3,72</t>
+          <t>1,32; 3,8</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,2; 3,14</t>
+          <t>1,22; 3,16</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,55; 4,46</t>
+          <t>2,49; 4,45</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,91; 5,07</t>
+          <t>2,88; 5,13</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,95; 3,78</t>
+          <t>2,05; 3,91</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,95; 3,74</t>
+          <t>1,92; 3,82</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>9,93; 16,02</t>
+          <t>9,96; 16,01</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>9,2; 14,82</t>
+          <t>9,15; 14,55</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11,31; 16,76</t>
+          <t>11,37; 17,14</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,69; 15,9</t>
+          <t>4,72; 15,96</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>8,19; 13,72</t>
+          <t>8,08; 13,41</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,7; 16,47</t>
+          <t>10,67; 16,49</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,15; 11,92</t>
+          <t>7,3; 11,83</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>9,77; 14,75</t>
+          <t>9,81; 14,75</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>9,89; 13,64</t>
+          <t>9,87; 13,94</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>10,56; 14,54</t>
+          <t>10,69; 14,42</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>9,8; 13,5</t>
+          <t>9,82; 13,67</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>6,72; 14,07</t>
+          <t>7,26; 14,24</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>25,86; 35,18</t>
+          <t>25,83; 35,25</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>30,58; 40,06</t>
+          <t>30,73; 40,51</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>18,65; 26,62</t>
+          <t>18,35; 26,5</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>25,04; 32,34</t>
+          <t>24,88; 31,91</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>27,73; 36,71</t>
+          <t>28,22; 37,09</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>35,38; 44,75</t>
+          <t>35,35; 44,86</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>26,05; 34,68</t>
+          <t>25,85; 34,92</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>22,71; 28,0</t>
+          <t>22,69; 28,13</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>27,99; 34,84</t>
+          <t>28,02; 34,49</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>34,4; 41,16</t>
+          <t>34,27; 41,3</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>23,35; 29,45</t>
+          <t>23,51; 29,39</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>24,81; 29,12</t>
+          <t>24,63; 29,02</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>32,92; 44,36</t>
+          <t>33,39; 44,12</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>45,04; 56,68</t>
+          <t>44,78; 56,99</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>36,56; 48,24</t>
+          <t>36,72; 47,59</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>43,43; 51,55</t>
+          <t>43,36; 51,76</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>40,8; 50,97</t>
+          <t>40,45; 50,4</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>51,13; 61,97</t>
+          <t>51,32; 62,54</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>39,97; 50,12</t>
+          <t>39,94; 50,76</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>43,94; 84,43</t>
+          <t>44,09; 83,25</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>38,83; 46,1</t>
+          <t>38,78; 46,45</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>50,22; 58,17</t>
+          <t>50,17; 57,95</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>40,05; 47,45</t>
+          <t>40,01; 47,55</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>45,96; 79,58</t>
+          <t>45,41; 77,52</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>40,59; 53,95</t>
+          <t>40,62; 54,39</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>52,07; 65,75</t>
+          <t>52,44; 65,9</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>49,11; 60,49</t>
+          <t>49,79; 60,66</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>53,08; 61,91</t>
+          <t>52,47; 62,19</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>50,76; 61,95</t>
+          <t>50,67; 62,27</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>59,43; 69,61</t>
+          <t>59,24; 69,38</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>51,86; 62,52</t>
+          <t>51,36; 63,19</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>61,2; 67,79</t>
+          <t>61,38; 68,08</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>47,85; 56,62</t>
+          <t>48,11; 56,94</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>58,43; 66,67</t>
+          <t>58,84; 66,75</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>52,3; 60,16</t>
+          <t>52,37; 60,62</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>58,94; 64,63</t>
+          <t>59,1; 64,77</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>11,59; 13,9</t>
+          <t>11,58; 13,72</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>15,25; 18,04</t>
+          <t>15,4; 18,05</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>13,68; 16,1</t>
+          <t>13,69; 16,22</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>13,67; 19,62</t>
+          <t>13,55; 19,44</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>15,41; 18,08</t>
+          <t>15,54; 18,01</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>19,62; 22,32</t>
+          <t>19,56; 22,47</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>16,43; 19,11</t>
+          <t>16,43; 19,07</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>19,8; 39,36</t>
+          <t>19,73; 37,9</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>13,84; 15,6</t>
+          <t>13,86; 15,63</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>17,85; 19,77</t>
+          <t>17,93; 19,84</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>15,46; 17,33</t>
+          <t>15,44; 17,24</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>18,5; 30,12</t>
+          <t>18,35; 30,39</t>
         </is>
       </c>
     </row>
@@ -1810,7 +1810,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicinas para la tensión arterial en las dos últimas semanas</t>
+          <t>Población que ha consumido medicinas para la tensión arterial en las dos últimas semanas (tasa de respuesta: 99,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 3879</t>
+          <t>0; 3929</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 5384</t>
+          <t>0; 4829</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 2044</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 901</t>
+          <t>0; 853</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 1832</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 1958</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 4531</t>
+          <t>0; 4524</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 7974</t>
+          <t>0; 8892</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 3684</t>
+          <t>0; 4366</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0; 7100</t>
+          <t>0; 4559</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0; 3999</t>
+          <t>0; 4533</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>158; 10235</t>
+          <t>0; 10351</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 5401</t>
+          <t>0; 6228</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2830; 14136</t>
+          <t>2351; 13822</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1945; 13073</t>
+          <t>1975; 12248</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 7135</t>
+          <t>0; 7073</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1758; 10299</t>
+          <t>1759; 10723</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3798; 17593</t>
+          <t>3819; 16823</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 6659</t>
+          <t>0; 6671</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1624; 10766</t>
+          <t>1261; 10798</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2777; 13686</t>
+          <t>2772; 13038</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>8003; 27278</t>
+          <t>8683; 26515</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2937; 15586</t>
+          <t>2930; 14733</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2629; 13191</t>
+          <t>2939; 13448</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>10450; 25853</t>
+          <t>9520; 25451</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>21346; 43636</t>
+          <t>21267; 43897</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>13017; 31016</t>
+          <t>13288; 31839</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>11718; 29343</t>
+          <t>11093; 28896</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>19260; 40040</t>
+          <t>19484; 40023</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>14442; 33004</t>
+          <t>14555; 33033</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8833; 24572</t>
+          <t>8725; 25153</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>6492; 17036</t>
+          <t>6621; 17153</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>33913; 59260</t>
+          <t>32989; 59112</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>40359; 70246</t>
+          <t>39853; 71099</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>25961; 50321</t>
+          <t>27269; 52028</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>20994; 40362</t>
+          <t>20740; 41259</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>51571; 83158</t>
+          <t>51712; 83097</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>56574; 91070</t>
+          <t>56212; 89400</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>73053; 108268</t>
+          <t>73478; 110753</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>41598; 141196</t>
+          <t>41867; 141651</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>42227; 70737</t>
+          <t>41673; 69127</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>65702; 101145</t>
+          <t>65505; 101241</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>46429; 77341</t>
+          <t>47372; 76798</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>69646; 105141</t>
+          <t>69967; 105161</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>102301; 141163</t>
+          <t>102115; 144288</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>129698; 178671</t>
+          <t>131288; 177235</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>126878; 174794</t>
+          <t>127187; 177019</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>107566; 225258</t>
+          <t>116261; 227922</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>99990; 136043</t>
+          <t>99876; 136330</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>130993; 171578</t>
+          <t>131622; 173531</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>89122; 127200</t>
+          <t>87710; 126670</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>140265; 181164</t>
+          <t>139375; 178763</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>112042; 148307</t>
+          <t>113999; 149823</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>158031; 199876</t>
+          <t>157881; 200390</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>129407; 172308</t>
+          <t>128414; 173481</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>123745; 152587</t>
+          <t>123626; 153292</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>221302; 275517</t>
+          <t>221586; 272698</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>300967; 360133</t>
+          <t>299854; 361394</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>227598; 287074</t>
+          <t>229194; 286474</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>274141; 321833</t>
+          <t>272195; 320704</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>96329; 129781</t>
+          <t>97698; 129091</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>139533; 175576</t>
+          <t>138712; 176534</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>122224; 161277</t>
+          <t>122761; 159091</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>159504; 189318</t>
+          <t>159256; 190114</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>139901; 174803</t>
+          <t>138700; 172851</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>181012; 219375</t>
+          <t>181676; 221393</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>150995; 189324</t>
+          <t>150866; 191747</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>267297; 513650</t>
+          <t>268241; 506462</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>246743; 292983</t>
+          <t>246456; 295168</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>333383; 386145</t>
+          <t>333032; 384670</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>285201; 337878</t>
+          <t>284906; 338614</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>448424; 776384</t>
+          <t>443040; 756366</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>85188; 113226</t>
+          <t>85245; 114145</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>130107; 164280</t>
+          <t>131033; 164659</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>126216; 155457</t>
+          <t>127962; 155896</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>150079; 175055</t>
+          <t>148369; 175837</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>169479; 206868</t>
+          <t>169179; 207915</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>230468; 269951</t>
+          <t>229743; 269040</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>207510; 250187</t>
+          <t>205531; 252847</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>259934; 287901</t>
+          <t>260709; 289147</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>260200; 307902</t>
+          <t>261641; 309660</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>372590; 425088</t>
+          <t>375218; 425634</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>343726; 395374</t>
+          <t>344181; 398402</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>416989; 457233</t>
+          <t>418088; 458257</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>379776; 455223</t>
+          <t>379184; 449429</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>521960; 617425</t>
+          <t>527150; 617562</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>464438; 546579</t>
+          <t>464682; 550516</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>472651; 678362</t>
+          <t>468711; 672069</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>520780; 611006</t>
+          <t>525033; 608714</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>695928; 791566</t>
+          <t>693845; 796944</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>582339; 677238</t>
+          <t>582402; 675898</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>724417; 1439981</t>
+          <t>721775; 1386413</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>920899; 1037997</t>
+          <t>922669; 1040186</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1243721; 1377777</t>
+          <t>1249357; 1382581</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1072519; 1202296</t>
+          <t>1071688; 1196193</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>1316310; 2143246</t>
+          <t>1305539; 2162816</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P16A11-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P16A11-Edad-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,04%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,63%</t>
         </is>
       </c>
     </row>
@@ -722,7 +722,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,07</t>
+          <t>0,0; 0,96</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,21</t>
+          <t>0,0; 3,54</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -752,27 +752,27 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,84</t>
+          <t>0,0; 2,81</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,45</t>
+          <t>0,0; 0,35</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,52</t>
+          <t>0,0; 0,55</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,56</t>
+          <t>0,0; 0,51</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,45</t>
+          <t>0,0; 2,1</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,68%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,85</t>
+          <t>0,0; 0,96</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,34; 2,01</t>
+          <t>0,42; 2,16</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,33; 2,07</t>
+          <t>0,33; 2,16</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,67</t>
+          <t>0,0; 1,44</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,28; 1,71</t>
+          <t>0,3; 1,7</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,63; 2,76</t>
+          <t>0,6; 2,9</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,18</t>
+          <t>0,0; 1,14</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,25; 2,11</t>
+          <t>0,36; 2,07</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,2; 0,96</t>
+          <t>0,2; 1,02</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,67; 2,05</t>
+          <t>0,66; 2,05</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,25; 1,28</t>
+          <t>0,31; 1,34</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,31; 1,44</t>
+          <t>0,3; 1,41</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,81%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,49; 3,99</t>
+          <t>1,56; 4,04</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,13; 6,45</t>
+          <t>3,03; 6,51</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,99; 4,76</t>
+          <t>1,9; 4,79</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,07; 5,39</t>
+          <t>2,19; 5,44</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,82; 5,8</t>
+          <t>2,79; 5,77</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,06; 4,68</t>
+          <t>2,11; 4,77</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,32; 3,8</t>
+          <t>1,43; 3,81</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,22; 3,16</t>
+          <t>1,21; 3,1</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,49; 4,45</t>
+          <t>2,46; 4,54</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,88; 5,13</t>
+          <t>2,88; 5,01</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,05; 3,91</t>
+          <t>1,94; 3,74</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,92; 3,82</t>
+          <t>1,97; 3,81</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>14,04%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>13,09%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>9,96; 16,01</t>
+          <t>9,82; 15,87</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>9,15; 14,55</t>
+          <t>9,33; 14,64</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11,37; 17,14</t>
+          <t>10,78; 16,56</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,72; 15,96</t>
+          <t>11,77; 16,91</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>8,08; 13,41</t>
+          <t>8,0; 13,4</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,67; 16,49</t>
+          <t>10,85; 16,4</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,3; 11,83</t>
+          <t>7,28; 12,18</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>9,81; 14,75</t>
+          <t>10,4; 14,28</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>9,87; 13,94</t>
+          <t>9,77; 13,72</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>10,69; 14,42</t>
+          <t>10,71; 14,66</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>9,82; 13,67</t>
+          <t>9,83; 13,5</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>7,26; 14,24</t>
+          <t>11,59; 14,93</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>28,34%</t>
+          <t>27,73%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>25,17%</t>
+          <t>25,72%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>26,78%</t>
+          <t>26,73%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>25,83; 35,25</t>
+          <t>25,63; 35,55</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>30,73; 40,51</t>
+          <t>30,95; 40,75</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>18,35; 26,5</t>
+          <t>18,51; 26,72</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>24,88; 31,91</t>
+          <t>24,66; 31,43</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>28,22; 37,09</t>
+          <t>27,86; 37,15</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>35,35; 44,86</t>
+          <t>35,04; 44,65</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>25,85; 34,92</t>
+          <t>25,85; 34,33</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>22,69; 28,13</t>
+          <t>23,22; 28,39</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>28,02; 34,49</t>
+          <t>28,16; 34,87</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>34,27; 41,3</t>
+          <t>34,42; 41,37</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>23,51; 29,39</t>
+          <t>23,44; 29,25</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>24,63; 29,02</t>
+          <t>24,49; 28,93</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>47,8%</t>
+          <t>46,84%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>63,79%</t>
+          <t>46,09%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>57,77%</t>
+          <t>46,45%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>33,39; 44,12</t>
+          <t>33,12; 44,2</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>44,78; 56,99</t>
+          <t>45,12; 57,56</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>36,72; 47,59</t>
+          <t>36,73; 47,24</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>43,36; 51,76</t>
+          <t>42,48; 51,03</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>40,45; 50,4</t>
+          <t>40,62; 51,05</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>51,32; 62,54</t>
+          <t>51,86; 62,25</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>39,94; 50,76</t>
+          <t>40,15; 50,58</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>44,09; 83,25</t>
+          <t>42,76; 49,79</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>38,78; 46,45</t>
+          <t>38,86; 46,21</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>50,17; 57,95</t>
+          <t>50,11; 57,92</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>40,01; 47,55</t>
+          <t>39,67; 47,31</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>45,41; 77,52</t>
+          <t>43,69; 48,91</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>57,65%</t>
+          <t>57,5%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>64,72%</t>
+          <t>64,45%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>61,89%</t>
+          <t>61,66%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>40,62; 54,39</t>
+          <t>39,89; 53,71</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>52,44; 65,9</t>
+          <t>53,23; 66,34</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>49,79; 60,66</t>
+          <t>49,14; 60,25</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>52,47; 62,19</t>
+          <t>52,92; 62,27</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>50,67; 62,27</t>
+          <t>50,35; 61,51</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>59,24; 69,38</t>
+          <t>59,35; 69,26</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>51,36; 63,19</t>
+          <t>51,22; 62,42</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>61,38; 68,08</t>
+          <t>61,1; 67,64</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>48,11; 56,94</t>
+          <t>48,24; 56,93</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>58,84; 66,75</t>
+          <t>58,93; 66,62</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>52,37; 60,62</t>
+          <t>52,09; 60,24</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>59,1; 64,77</t>
+          <t>59,1; 64,55</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>24,68%</t>
+          <t>20,53%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>21,3%</t>
+          <t>19,68%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>11,58; 13,72</t>
+          <t>11,61; 13,82</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>15,4; 18,05</t>
+          <t>15,38; 18,01</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>13,69; 16,22</t>
+          <t>13,57; 15,99</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>13,55; 19,44</t>
+          <t>17,52; 19,97</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>15,54; 18,01</t>
+          <t>15,53; 18,1</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>19,56; 22,47</t>
+          <t>19,46; 22,4</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>16,43; 19,07</t>
+          <t>16,42; 19,24</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>19,73; 37,9</t>
+          <t>19,48; 21,53</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>13,86; 15,63</t>
+          <t>13,76; 15,46</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>17,93; 19,84</t>
+          <t>17,93; 19,82</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>15,44; 17,24</t>
+          <t>15,46; 17,32</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>18,35; 30,39</t>
+          <t>18,86; 20,43</t>
         </is>
       </c>
     </row>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>169</t>
+          <t>2836</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1621</t>
+          <t>2032</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1790</t>
+          <t>4868</t>
         </is>
       </c>
     </row>
@@ -2068,12 +2068,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 3929</t>
+          <t>0; 3963</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 4829</t>
+          <t>0; 4347</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -2083,7 +2083,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 853</t>
+          <t>0; 14438</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2098,32 +2098,32 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 4524</t>
+          <t>0; 4525</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 8892</t>
+          <t>0; 10175</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 4366</t>
+          <t>0; 3381</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0; 4559</t>
+          <t>0; 4822</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0; 4533</t>
+          <t>0; 4186</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0; 10351</t>
+          <t>0; 16211</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1979</t>
+          <t>2130</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>4633</t>
+          <t>4557</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>6612</t>
+          <t>6687</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 6228</t>
+          <t>0; 7073</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2351; 13822</t>
+          <t>2878; 14791</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1975; 12248</t>
+          <t>1950; 12733</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 7073</t>
+          <t>0; 6887</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1759; 10723</t>
+          <t>1846; 10606</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3819; 16823</t>
+          <t>3668; 17639</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 6671</t>
+          <t>0; 6406</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1261; 10798</t>
+          <t>1795; 10386</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2772; 13038</t>
+          <t>2742; 13890</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>8683; 26515</t>
+          <t>8545; 26614</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2930; 14733</t>
+          <t>3568; 15429</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2939; 13448</t>
+          <t>2944; 13779</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>18593</t>
+          <t>22385</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>10876</t>
+          <t>12575</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>29469</t>
+          <t>34960</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>9520; 25451</t>
+          <t>9945; 25774</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>21267; 43897</t>
+          <t>20595; 44271</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>13288; 31839</t>
+          <t>12713; 32062</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>11093; 28896</t>
+          <t>13584; 33797</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>19484; 40023</t>
+          <t>19224; 39764</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>14555; 33033</t>
+          <t>14920; 33701</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8725; 25153</t>
+          <t>9484; 25205</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>6621; 17153</t>
+          <t>7533; 19297</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>32989; 59112</t>
+          <t>32635; 60324</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>39853; 71099</t>
+          <t>39848; 69399</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>27269; 52028</t>
+          <t>25853; 49751</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>20740; 41259</t>
+          <t>24467; 47310</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>95251</t>
+          <t>98393</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>85389</t>
+          <t>89723</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>180640</t>
+          <t>188116</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>51712; 83097</t>
+          <t>50994; 82371</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>56212; 89400</t>
+          <t>57350; 90007</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>73478; 110753</t>
+          <t>69613; 107004</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>41867; 141651</t>
+          <t>82484; 118470</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>41673; 69127</t>
+          <t>41273; 69078</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>65505; 101241</t>
+          <t>66601; 100687</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>47372; 76798</t>
+          <t>47283; 79059</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>69967; 105161</t>
+          <t>76617; 105256</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>102115; 144288</t>
+          <t>101065; 141950</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>131288; 177235</t>
+          <t>131605; 180121</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>127187; 177019</t>
+          <t>127301; 174863</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>116261; 227922</t>
+          <t>166667; 214616</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>158793</t>
+          <t>168719</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>137169</t>
+          <t>156242</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>295962</t>
+          <t>324961</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>99876; 136330</t>
+          <t>99115; 137466</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>131622; 173531</t>
+          <t>132579; 174548</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>87710; 126670</t>
+          <t>88455; 127707</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>139375; 178763</t>
+          <t>150016; 191218</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>113999; 149823</t>
+          <t>112561; 150096</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>157881; 200390</t>
+          <t>156535; 199443</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>128414; 173481</t>
+          <t>128414; 170592</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>123626; 153292</t>
+          <t>141069; 172442</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>221586; 272698</t>
+          <t>222684; 275708</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>299854; 361394</t>
+          <t>301163; 361993</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>229194; 286474</t>
+          <t>228523; 285085</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>272195; 320704</t>
+          <t>297756; 351688</t>
         </is>
       </c>
     </row>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>175550</t>
+          <t>190262</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>388067</t>
+          <t>202412</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>563617</t>
+          <t>392675</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>97698; 129091</t>
+          <t>96891; 129311</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>138712; 176534</t>
+          <t>139772; 178316</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>122761; 159091</t>
+          <t>122810; 157925</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>159256; 190114</t>
+          <t>172532; 207254</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>138700; 172851</t>
+          <t>139289; 175065</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>181676; 221393</t>
+          <t>183565; 220366</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>150866; 191747</t>
+          <t>151678; 191074</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>268241; 506462</t>
+          <t>187773; 218657</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>246456; 295168</t>
+          <t>246958; 293703</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>333032; 384670</t>
+          <t>332639; 384473</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>284906; 338614</t>
+          <t>282454; 336869</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>443040; 756366</t>
+          <t>369304; 413471</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>163003</t>
+          <t>178354</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>274886</t>
+          <t>298680</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>437889</t>
+          <t>477035</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>85245; 114145</t>
+          <t>83730; 112724</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>131033; 164659</t>
+          <t>132990; 165751</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>127962; 155896</t>
+          <t>126280; 154845</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>148369; 175837</t>
+          <t>164161; 193157</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>169179; 207915</t>
+          <t>168114; 205387</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>229743; 269040</t>
+          <t>230173; 268589</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>205531; 252847</t>
+          <t>204974; 249788</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>260709; 289147</t>
+          <t>283153; 313444</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>261641; 309660</t>
+          <t>262302; 309575</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>375218; 425634</t>
+          <t>375741; 424775</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>344181; 398402</t>
+          <t>342332; 395891</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>418088; 458257</t>
+          <t>457194; 499379</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>613339</t>
+          <t>663080</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>902641</t>
+          <t>766222</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>1515979</t>
+          <t>1429302</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>379184; 449429</t>
+          <t>380247; 452546</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>527150; 617562</t>
+          <t>526209; 616452</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>464682; 550516</t>
+          <t>460657; 542765</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>468711; 672069</t>
+          <t>618741; 705213</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>525033; 608714</t>
+          <t>524789; 611644</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>693845; 796944</t>
+          <t>690133; 794399</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>582402; 675898</t>
+          <t>581873; 681888</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>721775; 1386413</t>
+          <t>726964; 803573</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>922669; 1040186</t>
+          <t>915783; 1028937</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1249357; 1382581</t>
+          <t>1249622; 1381315</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1071688; 1196193</t>
+          <t>1072991; 1201570</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>1305539; 2162816</t>
+          <t>1369921; 1483872</t>
         </is>
       </c>
     </row>
